--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARCAÇA EXTERNA EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARCAÇA EXTERNA EMBREAGEM.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CARCAÇA EXTERNA EMBREAGEM IRON CG TITAN 2000 A 2004 KS/ FAN125 2005 A 2008 201217</t>
+          <t xml:space="preserve">CAMPANA EXTERNA EMBREAGEM IRON CG TITAN 2000 A 2004 KS/ FAN125 2005 A 2008 201217 </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CARCAÇA EXTERNA EMBREAGEM IRON FAN TITAN160/ START/ BROS NXR160 2015 201215</t>
+          <t>CAMPANA EXTERNA EMBREAGEM IRON FAN TITAN160/ START/ BROS NXR160 2015 201215</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -495,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CARCAÇA EXTERNA EMBREAGEM SMARTFOX FAZER150/ XTZ150/ FACTOR150</t>
+          <t>CAMPANA EXTERNA EMBREAGEM SMARTFOX FAZER150/ XTZ150/ FACTOR150</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -503,7 +507,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -516,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CARCAÇA EXTERNA EMBREAGEM IRON CG TITAN150 200 A 2008 KS/ BROS NXR150 2006 A 2014/ FAN125 2009 2013 201211</t>
+          <t>CAMPANA EXTERNA EMBREAGEM IRON CG TITAN150 200 A 2008 KS/ BROS NXR150 2006 A 2014/ FAN125 2009 2013 201211</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARCAÇA EXTERNA EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CARCAÇA EXTERNA EMBREAGEM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -530,11 +510,6 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>250</t>
         </is>
       </c>
     </row>
